--- a/output/output.xlsx
+++ b/output/output.xlsx
@@ -413,575 +413,631 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Unnamed: 0_x</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>customer_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>customer_name</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>customer_name_x</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>order_id</t>
+          <t>city_x</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>Unnamed: 0_y</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>customer_name_y</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>city_y</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>new_index_name_0</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>order_id_x</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>order_date</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>product_id</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>order_id_y</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>product_id_x</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
         <is>
           <t>quantity</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>product_id_y</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
         <is>
           <t>product_name</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>category</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>remarks</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Alice</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Alice</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
         <v>101</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>2026-01-10</t>
         </is>
       </c>
-      <c r="F2" t="n">
-        <v>1001</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Laptop</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Delivered successfully</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
+        <v>0</v>
+      </c>
+      <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Alice</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="D3" t="n">
-        <v>101</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-01-10</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>1002</v>
-      </c>
-      <c r="G3" t="n">
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Alice</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
         <v>2</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Mouse</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
+      <c r="I3" t="n">
+        <v>103</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Delivered successfully</t>
-        </is>
-      </c>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>1</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Alice</t>
-        </is>
+      <c r="B4" t="n">
+        <v>2</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>103</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-01-15</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>1005</v>
-      </c>
-      <c r="G4" t="n">
+          <t>Bob</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
         <v>1</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Headphones</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Bob</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>102</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Delayed due to weather</t>
-        </is>
-      </c>
+          <t>2026-01-11</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Alice</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="B5" t="n">
+        <v>3</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>112</v>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+          <t>Charlie</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Dallas</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Charlie</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dallas</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I5" t="n">
+        <v>104</v>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Awaiting payment</t>
-        </is>
-      </c>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Alice</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="B6" t="n">
+        <v>4</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New York</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>118</v>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+          <t>Diana</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Seattle</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Diana</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Seattle</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Order on hold</t>
-        </is>
-      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Bob</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="B7" t="n">
+        <v>5</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chicago</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>102</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-01-11</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>1003</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Desk</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Furniture</t>
-        </is>
+          <t>Ethan</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Boston</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ethan</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Boston</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>4</v>
+      </c>
+      <c r="I7" t="n">
+        <v>105</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Payment pending</t>
-        </is>
-      </c>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Bob</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="B8" t="n">
+        <v>6</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chicago</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>107</v>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+          <t>Fiona</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Miami</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Fiona</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Miami</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Order confirmed</t>
-        </is>
-      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>2</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Bob</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Chicago</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>113</v>
-      </c>
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="n">
+        <v>7</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+      <c r="H9" t="n">
+        <v>5</v>
+      </c>
+      <c r="I9" t="n">
+        <v>106</v>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Cancelled by customer</t>
-        </is>
-      </c>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="n">
-        <v>2</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Bob</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Chicago</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>119</v>
-      </c>
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Quality check completed</t>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="n">
+        <v>1001</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Laptop</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Electronics</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
-        <v>3</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Charlie</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Dallas</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>104</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-01-18</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>1004</v>
-      </c>
-      <c r="G11" t="n">
-        <v>4</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Chair</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Furniture</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Returned by customer</t>
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="n">
+        <v>1002</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Mouse</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Electronics</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
-        <v>3</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Charlie</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Dallas</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>108</v>
-      </c>
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Packed for shipment</t>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="n">
+        <v>1003</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Desk</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Furniture</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
-        <v>3</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Charlie</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Dallas</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>114</v>
-      </c>
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Refund initiated</t>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="n">
+        <v>1004</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Chair</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Furniture</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
-        <v>3</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Charlie</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Dallas</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>120</v>
-      </c>
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Ready for pickup</t>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="n">
+        <v>1005</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Headphones</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Electronics</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
-        <v>4</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Diana</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Seattle</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>109</v>
-      </c>
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Shipped</t>
-        </is>
-      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="n">
+        <v>101</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1001</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="n">
-        <v>4</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Diana</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Seattle</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>115</v>
-      </c>
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Replacement dispatched</t>
-        </is>
-      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="n">
+        <v>101</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1002</v>
+      </c>
+      <c r="M16" t="n">
+        <v>2</v>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" t="n">
-        <v>4</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Diana</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Seattle</t>
-        </is>
-      </c>
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
@@ -989,212 +1045,114 @@
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
+      <c r="K17" t="n">
+        <v>105</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1002</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3</v>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="n">
-        <v>5</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Ethan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Boston</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>105</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-01-20</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>1002</v>
-      </c>
-      <c r="G18" t="n">
-        <v>3</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Mouse</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Out for delivery</t>
-        </is>
-      </c>
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="n">
+        <v>102</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1003</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" t="n">
-        <v>5</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Ethan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Boston</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>110</v>
-      </c>
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>In transit</t>
-        </is>
-      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="n">
+        <v>104</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1004</v>
+      </c>
+      <c r="M19" t="n">
+        <v>4</v>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" t="n">
-        <v>5</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Ethan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Boston</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>116</v>
-      </c>
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>Delivery failed</t>
-        </is>
-      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="n">
+        <v>103</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1005</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1</v>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" t="n">
-        <v>6</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Fiona</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Miami</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>111</v>
-      </c>
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Delivered</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>6</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Fiona</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Miami</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>117</v>
-      </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>Rescheduled delivery</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>6</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Fiona</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Miami</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>7</v>
-      </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="n">
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="n">
         <v>106</v>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-01-25</t>
-        </is>
-      </c>
-      <c r="F24" t="n">
+      <c r="L21" t="n">
         <v>9999</v>
       </c>
-      <c r="G24" t="n">
+      <c r="M21" t="n">
         <v>1</v>
       </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>Customer not found</t>
-        </is>
-      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
